--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0097.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0097.xlsx
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Phụ "Huyền Thoại Đấu Trường Bóng Tối: Phần II" để nhận</t>
+          <t>Hoàn thành Nhiệm Vụ Phụ "Huyền Thoại Đấu Trường Bóng Tối: Phần II" để nhận được</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Phụ "Huyền Thoại Đấu Trường Bóng Tối: Phần III" để nhận</t>
+          <t>Hoàn thành Nhiệm Vụ Phụ "Huyền Thoại Đấu Trường Bóng Tối: Phần III" để nhận được</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>New Federation</t>
+          <t>Liên Bang Mới</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Startorch Academy</t>
+          <t>Học viện Startorch</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Radiant Spectrum</t>
+          <t>Phổ Quang Rực Rỡ</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Zhu Jing</t>
+          <t>Chu Tĩnh</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Choi Hyeon ji</t>
+          <t>Choi Hyeon Ji</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>New Federation</t>
+          <t>Liên Bang Mới</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Spacetrek Collective</t>
+          <t>Tập Đoàn Spacetrek</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Astral Mapping</t>
+          <t>Lập Bản Đồ Tinh Tú</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Oh Ro ah</t>
+          <t>Ôi Ro à...</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>"A New Journey"</t>
+          <t>"Hành Trình Mới"</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>"Unsanctioned" Mod Kit</t>
+          <t>"Bộ Mod Không Chính Thức"</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Cactus Pillow</t>
+          <t>Gối Xương Rồng</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Modified Starstack</t>
+          <t>Xếp Chồng Sao Đã Điều Chỉnh</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>"Gaze"</t>
+          <t>"Ánh Nhìn"</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Truancy Record</t>
+          <t>Hồ sơ Vắng Mặt</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Lurking Shadows</t>
+          <t>Bóng Tối Rình Rập</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Shifted Winds</t>
+          <t>Gió Dịch Chuyển</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Black and Gold</t>
+          <t>Đen và Vàng</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>A Thump</t>
+          <t>Ầm...</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Silent Duty</t>
+          <t>Thiên Trách Vô Thanh</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Admission Letter</t>
+          <t>Thư Nhập Học</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>The Stars</t>
+          <t>Những Vì Sao</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>And Vậy thì, Another Step</t>
+          <t>Và Rồi, Một Bước Tiếp Theo</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Apply</t>
+          <t>Áp dụng</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Huyền Thoại Đấu Bóng Tối: Phần I</t>
+          <t>Huyền Thoại Duel Hắc Ám: Phần I</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Huyền Thoại Đấu Bóng Tối: Phần II</t>
+          <t>Huyền Thoại Duel Hắc Ám: Phần II</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Huyền Thoại Đấu Bóng Tối: Phần III</t>
+          <t>Huyền Thoại Duel Hắc Ám: Phần III</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Chào mừng đến với Câu lạc bộ Người hâm mộ</t>
+          <t>Chào mừng đến với Câu Lạc Bộ Fan</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Thử Thách Đấu Sĩ: Lost Roya</t>
+          <t>Thử Thách Đấu Sĩ: Roya Lạc Lối</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Thử thách Tối thượng</t>
+          <t>Thử Thách Tối Thượng</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Thử thách Tối thượng</t>
+          <t>Thử Thách Tối Thượng</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Thử Thách Đấu Sĩ: Thành Viên Câu Lạc Bộ Tranh Luận</t>
+          <t>Thử Thách Đối Kháng: Thành Viên Câu Lạc Bộ Tranh Luận</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Squeezy không phải Smiley</t>
+          <t>Nén chứ không phải Cười</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Squeezy không phải Smiley</t>
+          <t>Nén chứ không phải Cười</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Nhà Nghiên Cứu Dịu Dàng</t>
+          <t>Nhà nghiên cứu dịu dàng</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Lost Roya</t>
+          <t>Roya Lạc Lối</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Passionate Duelist</t>
+          <t>Kẻ Đấu Sĩ Nồng Nhiệt</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Chengxi</t>
+          <t>Thành Hy</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Passive Tactic</t>
+          <t>Thụ Động Chiến Thuật</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Recharge Effect</t>
+          <t>Hiệu Ứng Nạp Năng Lượng</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Tổ Tacet</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Quick-Triển khai</t>
+          <t>Triển khai nhanh!</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Novelty</t>
+          <t>Vật phẩm Đặc Biệt</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Bắt Đầu Thử Thách</t>
+          <t>Bắt đầu Thử thách</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Singularity Expansion</t>
+          <t>Mở Rộng Điểm Kỳ Dị</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Sceneries</t>
+          <t>Cảnh vật</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Ghi Chép</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Qualified Duelist</t>
+          <t>Duelist Đủ Tiêu Chuẩn</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Certified Duelist</t>
+          <t>Duelist Chính Hiệu</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Certified Duelist</t>
+          <t>Duelist Chính Hiệu</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Promising Duelist</t>
+          <t>Duelist Giữ Lời</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Promising Duelist</t>
+          <t>Duelist Giữ Lời</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Experienced Duelist</t>
+          <t>Duelist Lão Luyện</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Experienced Duelist</t>
+          <t>Duelist Lão Luyện</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Popular Duelist</t>
+          <t>Đấu sĩ Nổi tiếng</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Popular Duelist</t>
+          <t>Đấu sĩ Nổi tiếng</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Veteran Duelist</t>
+          <t>Duelist Lão Thành</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Veteran Duelist</t>
+          <t>Duelist Lão Thành</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Tất cả-Star Duelist</t>
+          <t>Duelist Toàn Sao</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Tất cả-Star Duelist</t>
+          <t>Duelist Toàn Sao</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Legendary Duelist</t>
+          <t>Đấu Sĩ Huyền Thoại</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Legendary Duelist</t>
+          <t>Đấu Sĩ Huyền Thoại</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Legendary Duelist</t>
+          <t>Đấu Sĩ Huyền Thoại</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Legendary Duelist</t>
+          <t>Đấu Sĩ Huyền Thoại</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Legendary Duelist</t>
+          <t>Đấu Sĩ Huyền Thoại</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Vật phẩm mới phải được đặt trong Khu vực Triển khai</t>
+          <t>Vật phẩm Đặc Biệt phải đặt trong Vùng Triển Khai</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Không thể Điều chế Vật phẩm mới</t>
+          <t>Không Thể Điều Chỉnh Mới Lạ</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Sự kiện "Đỉnh Uy Danh: Trận Tái Đấu" để mở khóa</t>
+          <t>Hoàn thành Sự Kiện "Đỉnh Danh Vọng: Cuộc Đọ Sức Nảy Lửa" để mở khóa</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Chuyển đổi</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Hành Trình Reprise</t>
+          <t>Hành Trình Tái Ngộ</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Nội dung nổi bật</t>
+          <t>Nội Dung Nổi Bật</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Tăng Gấp Đôi Rơi Vật Phẩm</t>
+          <t>Nhân Đôi Rơi Vật Phẩm</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Hỗ Trợ Lên Cấp</t>
+          <t>Hỗ trợ Tăng cấp</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Đăng nhập 7 ngày</t>
+          <t>Đăng Nhập 7 Ngày</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Wuthering Triệu Tập</t>
+          <t>Hội Tụ Vực Gió</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Permanent</t>
+          <t>Vĩnh viễn</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Truy cập sớm giới hạn thời gian</t>
+          <t>Truy Cập Sớm Giới Hạn Thời Gian</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Event Exclusive</t>
+          <t>Sự kiện độc quyền</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Cấp Độ Điều chế</t>
+          <t>Cấp Độ Nâng Cấp</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Báo cáo Thám hiểm Hiệp hội Tiên phong, Khu vực Lahai-Roi - Trích đoạn I</t>
+          <t>Báo Cáo Thám Hiểm Hiệp Hội Tiên Phong, Khu Vực Lahai-Roi - Trích Đoạn I</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Báo cáo Thám hiểm Hiệp hội Tiên phong, Khu vực Lahai-Roi - Trích đoạn II</t>
+          <t>Báo Cáo Thám Hiểm Hiệp Hội Tiên Phong, Khu Vực Lahai-Roi - Trích Đoạn II</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Royan Formulae Transcripts - Preface I</t>
+          <t>Bản ghi công thức Roya - Lời tựa I</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Royan Formulae Transcripts - Preface I</t>
+          <t>Bản ghi công thức Roya - Lời tựa I</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>"Nơi Glommoth Từng Lang Thang" (Trích đoạn I)</t>
+          <t>"*Nơi Glommoth Từng Lang Thang* (Trích đoạn I)"</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>"Nơi Glommoth Từng Lang Thang" (Trích đoạn II)</t>
+          <t>"Nơi Glommoth Từng Lang Thang" (Trích Đoạn II)</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Nghiên cứu Lịch sử Royan (Trích đoạn I)</t>
+          <t>Lịch Sử Royan Qua Lăng Kính (Trích Đoạn I)</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Nghiên cứu Lịch sử Royan (Trích đoạn II)</t>
+          <t>Lịch Sử Royan Qua Lăng Kính (Trích Đoạn II)</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Bản ghi Âm thanh: Hội đồng Tái cấu trúc Tập thể Polar (Chưa công bố)</t>
+          <t>Bản Ghi Âm: Hội Đồng Tái Cấu Trúc Khối Cực Bắc (Chưa Công Bố)</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Sổ tay Sinh viên Học viện Startorch: Hướng dẫn Định hướng (Trích đoạn)</t>
+          <t>Sổ tay Sinh viên Học viện Startorch: Hướng dẫn Nhập học (Trích đoạn)</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Nhật ký Đầu cuối được phục hồi từ thành viên đoàn thám hiểm sa mạc Mawburrow đã mất</t>
+          <t>Nhật Ký Thiết Bị Đầu Cuối Thu Thập Từ Thành Viên Đoàn Thám Hiểm Sa Mạc Mawburrow Đã Mất Tích</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>"Nghiên cứu Thần thoại Royan" (Trích đoạn)</t>
+          <t>"Nghiên Cứu Về Thần Thoại Royan" (Trích đoạn)</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>"Khái niệm Thời gian của Royan" (Trích đoạn)</t>
+          <t>"Khái Niệm Thời Gian Của Người Royan" (Trích đoạn)</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Đạt 10.000 điểm trong Stability Accords để mở khóa</t>
+          <t>Đạt 10.000 điểm trong Hiệp Ước Ổn Định để mở khóa</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Không thể chọn Core Echo</t>
+          <t>Không thể chọn Tâm Âm Hạch</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Không thể chọn Domain</t>
+          <t>Không thể chọn Tổ Tacet</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Progress Tasks</t>
+          <t>Nhiệm vụ Tiến triển</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Nhiệm vụ Thử thách</t>
+          <t>Nhiệm Vụ Thử Thách</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Sự kiện này đã kết thúc</t>
+          <t>Sự kiện đã chấm dứt</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Mở khóa nút điều kiện tiên quyết trước</t>
+          <t>Hãy mở khóa nút điều kiện trước</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Hoàn thành Track Thường 2 để mở khóa</t>
+          <t>Hoàn thành Đường Đua Thường 2 để mở khóa</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Hoàn thành Track Thường 4 để mở khóa</t>
+          <t>Hoàn thành Đường Đua Thường 4 để mở khóa</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Hoàn thành Track Thường 6 để mở khóa</t>
+          <t>Hoàn thành Đường Đua Thường 6 để mở khóa</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Overclocking - Main Weapon I</t>
+          <t>Quá Tải - Vũ Khí Chính I</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Vitality Boost I</t>
+          <t>Tăng Sinh Lực I</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Overclocking - Main Weapon II</t>
+          <t>Quá Tải - Vũ Khí Chính II</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Overclocking - Hỗ Trợ Droid I</t>
+          <t>Quá Tải - Droid Hỗ Trợ I</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Vitality Boost II</t>
+          <t>Tăng Sinh Lực II</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Agile Iteration - Main Weapon I</t>
+          <t>Lặp Lại Linh Hoạt - Vũ Khí Chính I</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Overclocking - Hỗ Trợ Droid II</t>
+          <t>Quá Tải - Droid Hỗ Trợ II</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Safety Buffer</t>
+          <t>Vùng Đệm An Toàn</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Overclocking - Main Weapon III</t>
+          <t>Quá Tải - Vũ Khí Chính III</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Overclocking - Hỗ Trợ Droid III</t>
+          <t>Quá Tải - Droid Hỗ Trợ III</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Tough Choice</t>
+          <t>Lựa Chọn Khắc Nghiệt</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Vitality Boost III</t>
+          <t>Tăng Sinh Lực III</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Agile Iteration - Main Weapon II</t>
+          <t>Lặp Lại Linh Hoạt - Vũ Khí Chính II</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Agile Iteration - Hỗ Trợ Droid I</t>
+          <t>Lặp Lại Linh Hoạt - Droid Hỗ Trợ I</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Data Loop</t>
+          <t>Vòng lặp dữ liệu</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Orbital Strike - Trial Version</t>
+          <t>Đòn Đánh Quỹ Đạo - Bản Dùng Thử</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Agile Iteration - Hỗ Trợ Droid II</t>
+          <t>Lặp Lại Linh Hoạt - Droid Hỗ Trợ II</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Launch Control</t>
+          <t>Kiểm soát phóng</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Vitality Boost IV</t>
+          <t>Tăng Sinh Lực IV</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Agile Iteration - Main Weapon III</t>
+          <t>Lặp Lại Linh Hoạt - Vũ Khí Chính III</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Agile Iteration - Hỗ Trợ Droid III</t>
+          <t>Lặp Lại Linh Hoạt - Droid Hỗ Trợ III</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Overclocking - Hỗ Trợ Droid III</t>
+          <t>Quá Tải - Droid Hỗ Trợ III</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Code Refactoring</t>
+          <t>Tối Ưu Mã Lệnh</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Overclocking - Main Weapon III</t>
+          <t>Quá Tải - Vũ Khí Chính III</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Kích hoạt Boost khi bắt đầu thử thách</t>
+          <t>Kích hoạt Tăng Cường ngay khi thử thách bắt đầu</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>[Always Got a Choice]</t>
+          <t>Luôn có sự lựa chọn</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>[Weapon Analysis]</t>
+          <t>Phân Tích Vũ Khí</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,8 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>[Professional Medic]</t>
+          <t>[
+Y Sĩ Chuyên Nghiệp]</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25075,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Main Weapon</t>
+          <t>Vũ Khí Chính</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25145,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Hỗ Trợ Droid</t>
+          <t>Droid Hỗ Trợ</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25215,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Chung</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25285,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>"Perfect Beat"</t>
+          <t>"Nhịp Hoàn Hảo"</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25355,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Overloaded Energy Cube</t>
+          <t>Khối Năng Lượng Quá Tải</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25425,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Lớp phủ Giai đoạn Suy yếu</t>
+          <t>Lớp Phủ Pha Suy Yếu</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25495,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>The Ultimate Lucky Dice</t>
+          <t>Xúc Xắc May Mắn Tối Thượng</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25565,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>"Rhythm Injector" Medical Kit</t>
+          <t>"Bộ Tiêm Nhịp" Bộ Dụng Cụ Y Tế</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25635,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Dynamic Weak Point Detector</t>
+          <t>Bộ Phát Hiện Điểm Yếu Động</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25705,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Frequency Syntony Ampliflier</t>
+          <t>Bộ Khuếch Đại Cộng Hưởng Tần Số</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25775,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>"Burglar" Program Chip</t>
+          <t>"Chip Chương Trình 'Kẻ Trộm'"</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25845,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>"Clearing Master" Trophy</t>
+          <t>"Huy hiệu 'Bậc Thầy Dọn Dẹp'"</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25915,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Training Protocol Enhancement Key</t>
+          <t>Chìa khóa Nâng cấp Giao thức Huấn luyện</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25985,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Non-Euclid Scope</t>
+          <t>Kính Ngắm Phi Euclid</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26055,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Global Wave Amplifier</t>
+          <t>Bộ Khuếch Đại Sóng Toàn Cầu</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26125,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Blazing Chord</t>
+          <t>Hợp Âm Blaze</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26195,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Protocol Range Extender</t>
+          <t>Bộ Khuếch Đại Giao Thức</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26265,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Gashclaw</t>
+          <t>Móng Vuốt Sắc</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26335,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Lance of Death</t>
+          <t>Thương Tử Thần.</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26405,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Assault Gel</t>
+          <t>Gel Tấn Công</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26475,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>"Mother of Success"</t>
+          <t>"Mẹ của Thành Công"</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26545,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Mirror Terminal</t>
+          <t>Thiết bị Đầu cuối Gương</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26615,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Reinforcement Beacon</t>
+          <t>Đèn Hiệu Tăng Cường</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26685,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Ever-Instant Noodle</t>
+          <t>Mì Ăn Liền Vĩnh Cửu</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26755,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Refreshing Cold Drink</t>
+          <t>Thức uống mát lạnh</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26825,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Draining Dagger</t>
+          <t>Dao Hút Năng Lượng</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26895,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Unstable Gift</t>
+          <t>Món Quà Bất Ổn</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26965,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Ram Barrier</t>
+          <t>Hàng Rào Đâm</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27035,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Entropic Talisman</t>
+          <t>Bùa Hỗn Độn</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27105,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Soothing Fragrance</t>
+          <t>Hương Thơm Dịu Dàng</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27175,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Mucilage of Life</t>
+          <t>Dung Nham Sinh Mệnh</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27245,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Emergent Scaling</t>
+          <t>Tăng Trưởng Nhanh</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27315,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Seething Cake</t>
+          <t>Bánh Kem Giận Dữ</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27385,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Brittle Amplifier</t>
+          <t>Bộ Khuếch Đại Giòn Vỡ</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27455,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>One-Time Gun Cooler</t>
+          <t>Bình Làm Mát Súng Dùng Một Lần</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27525,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Precise Timer</t>
+          <t>Bộ Đếm Chính Xác</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27595,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Scrapped Cooling Valve</t>
+          <t>Van Làm Mát Hỏng</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27665,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Timed Deflector</t>
+          <t>Khiên Phản Đòn Có Hẹn Giờ</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27735,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Canned Chaos</t>
+          <t>Hỗn Loạn Đóng Hộp</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27805,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Grilled Fern Spore - Bổ Sung Bitter</t>
+          <t>Bào Tử Dương Xỉ Nướng - Vị Đắng Đặc Biệt</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27875,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Red Hot Shock</t>
+          <t>Sốc Nóng Đỏ</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27945,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Oscillating Disintegrator</t>
+          <t>Bộ Phân Rã Dao Động</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28015,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Balanced Stew</t>
+          <t>Món hầm cân bằng</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28085,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Rapidly Cooled Sweetness</t>
+          <t>Ngọt Lạnh Tức Thì</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28155,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Energy Maintenance Tank</t>
+          <t>Bể Bảo Dưỡng Năng Lượng</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28225,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Unbalanced Present</t>
+          <t>Hiện Tại Mất Cân Bằng</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28295,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Auxiliary Calibration Lens</t>
+          <t>Thấu Kính Hiệu Chỉnh Phụ Trợ</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28365,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Void Protein Jelly</t>
+          <t>Thạch Thể Protein Hư Không</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28435,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Chewy Lichen</t>
+          <t>Địa y dai nhách</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28505,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>"Virtuous Cycle"</t>
+          <t>"Vòng Luân Hồi Tốt Đẹp"</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28575,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>"Multiplier Extract"</t>
+          <t>"Chiết Xuất Hệ Số"</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28645,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Momentum Gear</t>
+          <t>Bánh Răng Đà Tiến</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28715,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Efficiency Repair Box</t>
+          <t>Hộp Sửa Chữa Hiệu Suất</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28785,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Canned Chaos</t>
+          <t>Hỗn Loạn Đóng Hộp</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28855,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Data Extraction: Mourning Aix</t>
+          <t>Trích Xuất Dữ Liệu: Mourning Aix</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28925,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Data Extraction: Lampylumen Myriad</t>
+          <t>Trích Xuất Dữ Liệu: Lampylumen Myriad</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28995,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Data Extraction: Sentry Construct</t>
+          <t>Trích xuất dữ liệu: Sentry Construct</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29065,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29135,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Vui lòng hoàn thành track tiên quyết trước</t>
+          <t>Hãy hoàn thành đường đua tiên quyết trước đã.</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29205,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Main Weapon Stats</t>
+          <t>Chỉ Số Vũ Khí Chính</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29275,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Hỗ Trợ Droid Stats</t>
+          <t>Chỉ Số Vận Mệnh Giả Hỗ Trợ</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29345,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>General Stats</t>
+          <t>Thông số Đại tướng</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29415,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Khiên</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29485,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Shield Bonus</t>
+          <t>Thêm Khiên</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29555,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Life Drain</t>
+          <t>Hút Sinh Lực</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29625,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Healing Bonus</t>
+          <t>Tăng Hiệu Quả Hồi Phục</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29695,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Basic Healing</t>
+          <t>Hồi Phục Cơ Bản</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29765,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>SPD</t>
+          <t>TỐC ĐỘ</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29835,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Hỗ Trợ Droid Quantity</t>
+          <t>Số Lượng Vận Mệnh Giả Hỗ Trợ</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29905,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Thử thách Track Vô tận để giành thứ hạng trên bảng xếp hạng</t>
+          <t>Thử Thách Vô Tận - Chứng tỏ đẳng cấp trên bảng xếp hạng</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29975,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Clear Thường Track 2</t>
+          <t>Hoàn thành Đường Đua Thường 2</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30045,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Clear Thường Track 4</t>
+          <t>Hoàn thành Đường Đua Thường 4</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30115,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Clear Thường Track 6</t>
+          <t>Hoàn thành Đường Đua Thường 6</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30185,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Thường Track 1</t>
+          <t>Nhạc Thường 1</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30255,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Thường Track 2</t>
+          <t>Nhạc Thường 2</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30325,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Thường Track 3</t>
+          <t>Nhạc Thường 3</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30395,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Thường Track 4</t>
+          <t>Nhạc Thường 4</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30465,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Thường Track 5</t>
+          <t>Nhạc Thường 5</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30535,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Thường Track 6</t>
+          <t>Nhạc Thường 6</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30605,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Elite Track 1</t>
+          <t>Nhiệm vụ tinh nhuệ 1</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30675,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Elite Track 2</t>
+          <t>Nhiệm vụ tinh nhuệ 2</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30745,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Endless Track</t>
+          <t>Bản nhạc Vô Tận</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30815,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Data Projection: Mourning Aix</t>
+          <t>Dự Án Dữ liệu: Mourning Aix</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30885,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Data Projection: Lampylumen Myriad</t>
+          <t>Dự Án Dữ liệu: Lampylumen Myriad</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30955,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Data Projection: Sentry Construct</t>
+          <t>Dự Án Dữ liệu: Sentry Construct</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31025,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Data Projection: Kronaclaw</t>
+          <t>Dự Án Dữ liệu: Kronaclaw</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31095,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Data Projection: Hyvatia</t>
+          <t>Dự Án Dữ liệu: Hyvatia</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31165,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Data Projection: Twin Nova: Nebulous Cannon</t>
+          <t>Dự Án Dữ liệu: Twin Nova: Nebulous Cannon</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31235,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Data Projection: Twin Nova: Collapsar Blade</t>
+          <t>Dự Án Dữ liệu: Twin Nova: Collapsar Blade</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31305,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Clear Thường Track 3</t>
+          <t>Hoàn thành Đường Đua Thường 3</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31375,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Clear Thường Track 5</t>
+          <t>Hoàn thành Đường Đua Thường 5</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31514,7 +31515,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Selected</t>
+          <t>Đã chọn</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31585,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Phần thưởng Nhiệm vụ</t>
+          <t>Phần Thưởng Nhiệm Vụ</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31724,7 +31725,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Vui lòng kích hoạt Core Protocols hoặc thử các tổ hợp mạnh hơn</t>
+          <t>Hãy kích hoạt Giao Thức Lõi hoặc thử kết hợp mạnh hơn đi!</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31795,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Hoàn thành giai đoạn yêu cầu để mở khóa</t>
+          <t>Hoàn thành giai đoạn yêu cầu để mở khóa.</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31865,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Vòng</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31935,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Xuống trước khi tương tác</t>
+          <t>Xuống xe trước khi tương tác</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32005,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Tape of Last Words</t>
+          <t>Băng Lời Cuối</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32144,7 +32145,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Void Storm Zone</t>
+          <t>Khu Vực Bão Hư Không</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32215,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32285,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Hot Spring Stargazing</t>
+          <t>Ngắm Sao Suối Nước Nóng</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32355,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Route Constructor Racing Challenge</t>
+          <t>Thử Thách Đua Xe Xây Dựng Tuyến Đường</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32425,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Mechascout: Transition</t>
+          <t>Máy trinh sát cơ khí: Transition</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32495,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Motorbike Racing</t>
+          <t>Đua Xe Máy</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32565,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Nơi Ánh Sáng Hóa Hình</t>
+          <t>Nơi Ánh Sáng Hình Thành</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32635,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Giai Điệu Lạc Lối</t>
+          <t>Giai Điệu Lạc Khuất</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32705,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Treasure Spot</t>
+          <t>Điểm Kho Báu</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32844,7 +32845,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Nhận Resonator hoặc Vũ khí 5 Sao</t>
+          <t>Nhận một Resonator hoặc Vũ Khí 5 Sao</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32915,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Nhận Cúp</t>
+          <t>Nhận một Chiến tích</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32985,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Concealed Starlight</t>
+          <t>Ánh Sao Ẩn</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33055,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Law of Stars</t>
+          <t>Luật của Vì Sao</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33125,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Cosmic Spindle</t>
+          <t>Trục Xoay Vũ Trụ</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33195,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Đạt 3.000 Điểm Hành Trình để nhận</t>
+          <t>Đạt 3.000 Điểm Hành Trình để nhận thưởng</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33265,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Đạt 5.000 Điểm Hành Trình để nhận</t>
+          <t>Đạt 5.000 Điểm Hành Trình để nhận thưởng</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33335,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Đạt 10.000 Điểm Hành Trình để nhận</t>
+          <t>Đạt 10.000 Điểm Hành Trình để nhận thưởng.</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33405,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Stability Accords Progress</t>
+          <t>Tiến Độ Hiệp Ước Ổn Định</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33475,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Singularity Expansion Progress</t>
+          <t>Tiến Độ Mở Rộng Kỳ Dị</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33545,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Bạn phải là Bạn bè để chặn người chơi</t>
+          <t>Cậu phải là bạn bè mới chặn được người chơi chứ</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33615,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>To the Stars Yet to Shine</t>
+          <t>Đến Những Vì Sao Chưa Lóe Sáng</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33685,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Chọn một lá bài trên tay để xáo lại</t>
+          <t>Chọn một lá bài trên tay để xáo trộn lại</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33755,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>5-Star Echoes Only</t>
+          <t>Chỉ Cộng Hưởng Giả 5 Sao</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33825,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Không thể chơi Co-op</t>
+          <t>Chế Độ Hợp Tác Không Khả Dụng</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33895,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Hợp Nhất Chỉ Định</t>
+          <t>Hợp Nhất Có Mục Tiêu</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33965,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Tiêu Chuẩn Merge</t>
+          <t>Hợp nhất tiêu chuẩn</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34035,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Không còn lượt thử trong tuần này</t>
+          <t>Đã hết lượt trong tuần này</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34105,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Số lượt Merge mục tiêu đã được đặt lại, vui lòng vào lại</t>
+          <t>Số lần thử Hợp Nhất Có Mục Tiêu đã được đặt lại, hãy vào lại</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34175,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Tất cả-Terrain Tactics</t>
+          <t>Chiến Thuật Đa Địa Hình</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34245,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Snow Tires</t>
+          <t>Lốp Tuyết</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34315,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 4 Điểm Modding Đa Địa Hình</t>
+          <t>Tổng cộng thu thập 4 Điểm Nâng Cấp Địa Hình Toàn Diện.</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34385,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Low Temp. Ignition</t>
+          <t>Đánh Lửa Nhiệt Độ Thấp</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34455,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 8 Điểm Modding Đa Địa Hình</t>
+          <t>Thu thập tổng cộng 8 Điểm Nâng Cấp Địa Hình</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34525,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Firepower Aid</t>
+          <t>Hỗ Trợ Hỏa Lực</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34595,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 12 Điểm Modding Đa Địa Hình</t>
+          <t>Thu thập tổng cộng 12 Điểm Cải Tiến Địa Hình</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34665,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Gravity Well</t>
+          <t>Hố Trọng Lực</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34735,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Repulsion Wall</t>
+          <t>Bức Tường Đẩy</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34805,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Void Storm Zone - Enhanced Force Field</t>
+          <t>Khu Vực Bão Hư Không - Trường Lực Tăng Cường</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34875,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Void Storm Zone - Tune Break Boost</t>
+          <t>Khu Vực Bão Hư Không - Tăng Cường Phá Tần Số</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34945,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Assault Tech - Tune Rupture Enhanced</t>
+          <t>Công Nghệ Tấn Công - Tăng Cường Đột Phá Giai Điệu</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35015,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Tune Break Enhancement</t>
+          <t>Tăng Cường Phá Tần</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35085,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Assault Tech - Tune Strain Enhanced</t>
+          <t>Công Nghệ Tấn Công - Tăng Cường Áp Lực Giai Điệu</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35155,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Switch Mô-đun</t>
+          <t>Chuyển Module</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35225,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Vui lòng chọn Expansion Mô-đun muốn lắp đặt</t>
+          <t>Hãy chọn Mô-đun Mở Rộng muốn lắp đặt</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35295,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Đã lắp đặt</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35365,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Lắp đặt module này</t>
+          <t>Lắp mô-đun này vào</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35435,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Chuyển Đổi Mô-đun Mở Rộng</t>
+          <t>Chuyển đổi Mô-đun Mở rộng</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35505,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Danh sách Data Modification đã đầy</t>
+          <t>Danh sách Điều Chỉnh Dữ Liệu đã đầy</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
